--- a/artfynd/A 24362-2026 artfynd.xlsx
+++ b/artfynd/A 24362-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134416949</v>
       </c>
       <c r="B2" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134416807</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24362-2026 artfynd.xlsx
+++ b/artfynd/A 24362-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>134416949</v>
       </c>
       <c r="B2" t="n">
-        <v>96776</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134416807</v>
+        <v>134416989</v>
       </c>
       <c r="B3" t="n">
-        <v>98053</v>
+        <v>111153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575039</v>
+        <v>574974</v>
       </c>
       <c r="R3" t="n">
-        <v>6537719</v>
+        <v>6538074</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,6 +886,751 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134416871</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106199</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kolugnen O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575039</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6537719</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134416857</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kolugnen O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575039</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6537719</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134416807</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kolugnen O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575039</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6537719</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134416815</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kolugnen O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575039</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6537719</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134416714</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kolugnen O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575039</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6537719</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134416700</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kolugnen O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575039</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6537719</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134416887</v>
+      </c>
+      <c r="B10" t="n">
+        <v>107697</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224273</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig ängskovall</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. pratense</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kolugnen O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575039</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6537719</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24362-2026 artfynd.xlsx
+++ b/artfynd/A 24362-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416989</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416871</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416857</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416807</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416815</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416700</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,8 +1676,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134416887</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>